--- a/docs/Työajan seuranta Laura.xlsx
+++ b/docs/Työajan seuranta Laura.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juhaj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb667e905e7871ab/Documents/Git/movieproject/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42E345A2-8A07-4841-BEA8-AE5A2DA5432A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{42E345A2-8A07-4841-BEA8-AE5A2DA5432A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D40C2914-957A-40C0-9AA0-2C6DBB209C49}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11835" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Laura Similä" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
   <si>
     <t>Ryhmä:</t>
   </si>
@@ -148,16 +148,10 @@
     <t>Palaveria</t>
   </si>
   <si>
-    <t>0.75h</t>
-  </si>
-  <si>
     <t>23.9.</t>
   </si>
   <si>
     <t>Review- ja Favorites-tietokantatehtävien tilanteen tarkistus suhteessa nykyiseen tietokantaskeemaan</t>
-  </si>
-  <si>
-    <t>0.5h</t>
   </si>
   <si>
     <t>24.9.</t>
@@ -172,10 +166,25 @@
 Korjauksia ja bugitiketin teko</t>
   </si>
   <si>
-    <t>5.5h</t>
-  </si>
-  <si>
-    <t>PR Reviews käytetty aika (projektin aikana) ~ 6.25 h</t>
+    <t>27.9.</t>
+  </si>
+  <si>
+    <t>Seuraavan sprintin suunnittelu
+Tikettien työmääräarviointi
+Palaveria</t>
+  </si>
+  <si>
+    <t>28.9.</t>
+  </si>
+  <si>
+    <t>PR Reviews käytetty aika (projektin aikana) ~ 8.5 h</t>
+  </si>
+  <si>
+    <t>CI:n ESLint-tarkistuksen suunnittelu ja toteutus
+Palaveria</t>
+  </si>
+  <si>
+    <t>1.75 h</t>
   </si>
 </sst>
 </file>
@@ -211,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -224,6 +233,9 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -539,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD4D073-EB2D-44A2-86BF-660E3721AF80}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" customWidth="1"/>
@@ -698,29 +710,51 @@
         <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>38</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -729,20 +763,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -926,19 +960,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3DBD177-6275-4D31-B82C-61F9284D9B7B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/docs/Työajan seuranta Laura.xlsx
+++ b/docs/Työajan seuranta Laura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb667e905e7871ab/Documents/Git/movieproject/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{42E345A2-8A07-4841-BEA8-AE5A2DA5432A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D40C2914-957A-40C0-9AA0-2C6DBB209C49}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{42E345A2-8A07-4841-BEA8-AE5A2DA5432A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDA7B8AF-83F9-4439-84C9-F21EB3C21451}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>Ryhmä:</t>
   </si>
@@ -177,14 +177,24 @@
     <t>28.9.</t>
   </si>
   <si>
-    <t>PR Reviews käytetty aika (projektin aikana) ~ 8.5 h</t>
-  </si>
-  <si>
     <t>CI:n ESLint-tarkistuksen suunnittelu ja toteutus
 Palaveria</t>
   </si>
   <si>
     <t>1.75 h</t>
+  </si>
+  <si>
+    <t>29.9.</t>
+  </si>
+  <si>
+    <t>Implement Group Details Page – toteutuksen suunnittelu
+Implement Group Details Page – toteutus</t>
+  </si>
+  <si>
+    <t>2.75h</t>
+  </si>
+  <si>
+    <t>PR Reviews käytetty aika (projektin aikana) ~ 9 h</t>
   </si>
 </sst>
 </file>
@@ -252,6 +262,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -551,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD4D073-EB2D-44A2-86BF-660E3721AF80}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" customWidth="1"/>
@@ -584,7 +598,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -743,7 +757,7 @@
         <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -751,10 +765,21 @@
         <v>38</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -763,20 +788,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -960,19 +985,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3DBD177-6275-4D31-B82C-61F9284D9B7B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/docs/Työajan seuranta Laura.xlsx
+++ b/docs/Työajan seuranta Laura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb667e905e7871ab/Documents/Git/movieproject/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{42E345A2-8A07-4841-BEA8-AE5A2DA5432A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDA7B8AF-83F9-4439-84C9-F21EB3C21451}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{42E345A2-8A07-4841-BEA8-AE5A2DA5432A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0077216A-AB38-45F2-BD64-AD507DDFAFBE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
   <si>
     <t>Ryhmä:</t>
   </si>
@@ -191,10 +191,28 @@
 Implement Group Details Page – toteutus</t>
   </si>
   <si>
-    <t>2.75h</t>
-  </si>
-  <si>
-    <t>PR Reviews käytetty aika (projektin aikana) ~ 9 h</t>
+    <t>1.10.</t>
+  </si>
+  <si>
+    <t>PR Reviews käytetty aika (projektin aikana) ~ 9.25 h</t>
+  </si>
+  <si>
+    <t>2.75 h</t>
+  </si>
+  <si>
+    <t>Group movie removal -tarpeen määrittely
+Implement Removing Movies from Groups -ticketin määrittely</t>
+  </si>
+  <si>
+    <t>3.10.</t>
+  </si>
+  <si>
+    <t>Implement Removing Movies from Groups tiketin teko
+Group movie removal -integraatiotestit
+Group movie removal -UI:n optimointi</t>
+  </si>
+  <si>
+    <t>3 h</t>
   </si>
 </sst>
 </file>
@@ -565,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD4D073-EB2D-44A2-86BF-660E3721AF80}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" customWidth="1"/>
@@ -779,7 +797,29 @@
         <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>43</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -788,20 +828,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -985,19 +1025,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3DBD177-6275-4D31-B82C-61F9284D9B7B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/docs/Työajan seuranta Laura.xlsx
+++ b/docs/Työajan seuranta Laura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb667e905e7871ab/Documents/Git/movieproject/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{42E345A2-8A07-4841-BEA8-AE5A2DA5432A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0077216A-AB38-45F2-BD64-AD507DDFAFBE}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="8_{42E345A2-8A07-4841-BEA8-AE5A2DA5432A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97EE4E03-E1B0-481F-AD04-2F306DC729A7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B7036960-D674-4B76-B564-D076AACD5E6B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
   <si>
     <t>Ryhmä:</t>
   </si>
@@ -213,6 +213,32 @@
   </si>
   <si>
     <t>3 h</t>
+  </si>
+  <si>
+    <t>4.10.</t>
+  </si>
+  <si>
+    <t>Sprintin tilanteen läpikäynti
+Responsive UI- ja Optional Feature -backlog-tehtävien arviointi
+Palaveria</t>
+  </si>
+  <si>
+    <t>5.10.</t>
+  </si>
+  <si>
+    <t>REST API -dokumentointitavan selvitys
+Palaveria</t>
+  </si>
+  <si>
+    <t>6.10.</t>
+  </si>
+  <si>
+    <t>REST API Documentation -ticketin määrittely
+REST API Documentation -ticketin implementaatio
+Tiketin uudelleenteko Markdowniksi Postmanin vaikeuksien takia</t>
+  </si>
+  <si>
+    <t>1.25 h</t>
   </si>
 </sst>
 </file>
@@ -583,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BD4D073-EB2D-44A2-86BF-660E3721AF80}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" customWidth="1"/>
@@ -822,26 +848,59 @@
         <v>49</v>
       </c>
     </row>
+    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="44038759-07ae-40d4-bc3d-7c9fb0b3775b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1025,19 +1084,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3DBD177-6275-4D31-B82C-61F9284D9B7B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="44038759-07ae-40d4-bc3d-7c9fb0b3775b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28C42445-4535-4827-89B5-92D7D04A90E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
